--- a/etf_holdings/2026-10-08_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-08_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,33 +464,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00405A(15,000)、00993A(6,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00400A(-19,000)</t>
+          <t>00991A(-50,000)、00985A(-17,000)、00993A(-94,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,114 +499,114 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00400A(新納入)</t>
+          <t>00985A(16,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00993A(-67,000)</t>
+          <t>00993A(-26,000)、00400A(-45,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00992A(147,000)、00993A(8,000)</t>
+          <t>00985A(17,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-66,000)、00400A(-67,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(153,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00991A(-50,000)、00993A(-94,000)</t>
+          <t>00981A(-928,000)、00985A(-112,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(22,000)、00993A(6,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00992A(全數賣出)、00993A(-190,000)</t>
+          <t>00400A(-19,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(11,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00405A(-10,000)、00993A(-19,000)</t>
+          <t>00400A(-45,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(498,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00993A(-26,000)、00400A(-45,000)</t>
+          <t>00993A(-548,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -684,7 +684,517 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00993A(-66,000)、00400A(-67,000)</t>
+          <t>00985A(-16,000)、00993A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>00985A(-85,000)、00993A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00400A(新納入)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>00993A(-67,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00992A(147,000)、00993A(8,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00981A(321,000)、00403A(160,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00993A(112,000)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>00985A(-192,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>00992A(全數賣出)、00993A(-190,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00985A(11,000)、00993A(11,000)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>00985A(104,000)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>00981A(-579,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00993A(23,000)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>00985A(-34,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>00985A(-79,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>00981A(68,000)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>00993A(-19,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>00993A(48,000)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>00985A(-73,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>00985A(22,000)、00400A(135,000)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>00985A(317,000)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>00993A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>00985A(全數賣出)、00993A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>00403A(100,000)、00993A(89,000)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>00403A(-800,000)、00985A(-20,000)</t>
         </is>
       </c>
     </row>
